--- a/tests/electrico_nogal_apu.xlsx
+++ b/tests/electrico_nogal_apu.xlsx
@@ -52,7 +52,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -89,6 +89,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -117,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -181,6 +187,15 @@
     <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1950,7 +1965,7 @@
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leyenda: fila ÁMBAR = precio del archivo importado o tecleado a mano, sin APU de respaldo en el catálogo (suma al total y queda declarado). Fila ROJA = ítem sin precio: NO suma al total — un $0 sería un precio inventado.</t>
+          <t xml:space="preserve">Leyenda: fila SIN COLOR = precio de un contrato adjudicado (Nogal 4, 2025) servido en su misma región. Fila AMARILLA = precio con APU pero derivado por factor regional o estimado: no está verificado y requiere cotización. Fila ÁMBAR = precio del archivo importado o tecleado a mano, sin APU de respaldo en el catálogo (suma al total y queda declarado). Fila ROJA = ítem sin precio: NO suma al total — un $0 sería un precio inventado.</t>
         </is>
       </c>
     </row>

--- a/tests/electrico_nogal_apu.xlsx
+++ b/tests/electrico_nogal_apu.xlsx
@@ -210,12 +210,13 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="64" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -248,25 +249,30 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">CÓDIGO</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">DESCRIPCIÓN</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">UND.</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">CANT.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">VALOR UNITARIO</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">VALOR TOTAL</t>
         </is>
@@ -275,7 +281,7 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAFETERÍA</t>
+          <t xml:space="preserve">1. CAFETERÍA</t>
         </is>
       </c>
     </row>
@@ -287,23 +293,28 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.1</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro e instalación de tomacoriente monofásica normal de 15 A 120 V en canaleta metálica. Incluye: troquel metálico para toma eléctrica, cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje,
 transporte, marquilla de identificación y aseo diario.</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D7" s="21">
+      <c r="E7" s="21">
         <v>14</v>
       </c>
-      <c r="E7" s="16">
+      <c r="F7" s="16">
         <v>320488</v>
       </c>
-      <c r="F7" s="16">
-        <f>D7*E7</f>
+      <c r="G7" s="16">
+        <f>E7*F7</f>
         <v>4486832</v>
       </c>
     </row>
@@ -315,22 +326,27 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.2</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro e instalación de tomacoriente monofásica de 15 A 120 V, en muro, tubo PVC 1", tubo PVC 1/2", caja metálica Ref. 5800,  cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje, transporte,  marquilla de identificación y aseo diario.</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D8" s="21">
+      <c r="E8" s="21">
         <v>15</v>
       </c>
-      <c r="E8" s="16">
+      <c r="F8" s="16">
         <v>301516</v>
       </c>
-      <c r="F8" s="16">
-        <f>D8*E8</f>
+      <c r="G8" s="16">
+        <f>E8*F8</f>
         <v>4522740</v>
       </c>
     </row>
@@ -342,22 +358,27 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.3</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro e instalación de canaleta metalica calibre 20-22 con división, pintura electrostática de 15x5 cm, color blanca.</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">ML</t>
         </is>
       </c>
-      <c r="D9" s="21">
+      <c r="E9" s="21">
         <v>14</v>
       </c>
-      <c r="E9" s="16">
+      <c r="F9" s="16">
         <v>74596</v>
       </c>
-      <c r="F9" s="16">
-        <f>D9*E9</f>
+      <c r="G9" s="16">
+        <f>E9*F9</f>
         <v>1044344</v>
       </c>
     </row>
@@ -369,22 +390,27 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.4</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro e instalación de cable de cobre 3x12 trenzado AWG  LSZH azul</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">ML</t>
         </is>
       </c>
-      <c r="D10" s="21">
+      <c r="E10" s="21">
         <v>57</v>
       </c>
-      <c r="E10" s="16">
+      <c r="F10" s="16">
         <v>30172</v>
       </c>
-      <c r="F10" s="16">
-        <f>D10*E10</f>
+      <c r="G10" s="16">
+        <f>E10*F10</f>
         <v>1719804</v>
       </c>
     </row>
@@ -396,22 +422,27 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro e instalación de cable de cobre No 8  AWG  LSZH</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">ML</t>
         </is>
       </c>
-      <c r="D11" s="21">
+      <c r="E11" s="21">
         <v>20</v>
       </c>
-      <c r="E11" s="16">
+      <c r="F11" s="16">
         <v>26328</v>
       </c>
-      <c r="F11" s="16">
-        <f>D11*E11</f>
+      <c r="G11" s="16">
+        <f>E11*F11</f>
         <v>526560</v>
       </c>
     </row>
@@ -423,22 +454,27 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.6</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro e instalación de cable de cobre No 12 AWG LSZH</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">ML</t>
         </is>
       </c>
-      <c r="D12" s="21">
+      <c r="E12" s="21">
         <v>65</v>
       </c>
-      <c r="E12" s="16">
+      <c r="F12" s="16">
         <v>17552</v>
       </c>
-      <c r="F12" s="16">
-        <f>D12*E12</f>
+      <c r="G12" s="16">
+        <f>E12*F12</f>
         <v>1140880</v>
       </c>
     </row>
@@ -450,22 +486,27 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.7</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro e instalación de alambre de cobre desnudo No 14 AWG</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">ML</t>
         </is>
       </c>
-      <c r="D13" s="21">
+      <c r="E13" s="21">
         <v>150</v>
       </c>
-      <c r="E13" s="16">
+      <c r="F13" s="16">
         <v>14928</v>
       </c>
-      <c r="F13" s="16">
-        <f>D13*E13</f>
+      <c r="G13" s="16">
+        <f>E13*F13</f>
         <v>2239200</v>
       </c>
     </row>
@@ -477,22 +518,27 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.8</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro e instalación de breaker tipo industrial de 3*40 A de 1x20 A.</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D14" s="21">
+      <c r="E14" s="21">
         <v>1</v>
       </c>
-      <c r="E14" s="16">
+      <c r="F14" s="16">
         <v>81852</v>
       </c>
-      <c r="F14" s="16">
-        <f>D14*E14</f>
+      <c r="G14" s="16">
+        <f>E14*F14</f>
         <v>81852</v>
       </c>
     </row>
@@ -504,22 +550,27 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.9</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro e instalación de breaker tipo enchufable de 1x20 A.</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D15" s="21">
+      <c r="E15" s="21">
         <v>9</v>
       </c>
-      <c r="E15" s="16">
+      <c r="F15" s="16">
         <v>32908</v>
       </c>
-      <c r="F15" s="16">
-        <f>D15*E15</f>
+      <c r="G15" s="16">
+        <f>E15*F15</f>
         <v>296172</v>
       </c>
     </row>
@@ -531,22 +582,27 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.10</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suministro de tablero metálico trifásico de 18 circuitos  con espacio para totalizador.</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D16" s="21">
+      <c r="E16" s="21">
         <v>1</v>
       </c>
-      <c r="E16" s="16">
+      <c r="F16" s="16">
         <v>3129564</v>
       </c>
-      <c r="F16" s="16">
-        <f>D16*E16</f>
+      <c r="G16" s="16">
+        <f>E16*F16</f>
         <v>3129564</v>
       </c>
     </row>
@@ -558,22 +614,27 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.11</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Desconexión, desmonte y retiro tablero existente</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">GBL</t>
         </is>
       </c>
-      <c r="D17" s="21">
+      <c r="E17" s="21">
         <v>1</v>
       </c>
-      <c r="E17" s="16">
+      <c r="F17" s="16">
         <v>1529364</v>
       </c>
-      <c r="F17" s="16">
-        <f>D17*E17</f>
+      <c r="G17" s="16">
+        <f>E17*F17</f>
         <v>1529364</v>
       </c>
     </row>
@@ -585,1460 +646,1886 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.12</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Marquillaje e identificación</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">GBL</t>
         </is>
       </c>
-      <c r="D18" s="21">
+      <c r="E18" s="21">
         <v>1</v>
       </c>
-      <c r="E18" s="16">
+      <c r="F18" s="16">
         <v>2493992</v>
       </c>
-      <c r="F18" s="16">
-        <f>D18*E18</f>
+      <c r="G18" s="16">
+        <f>E18*F18</f>
         <v>2493992</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CAFETERÍA · SALIDAS ILUMINACIÓN</t>
-        </is>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal CAFETERÍA</t>
+        </is>
+      </c>
+      <c r="G19" s="14">
+        <f>SUM(G7:G18)</f>
+        <v>23211304</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. CAFETERÍA · SALIDAS ILUMINACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">2,1,1</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D20" s="21">
+      <c r="E21" s="21">
         <v>26</v>
       </c>
-      <c r="E20" s="16">
+      <c r="F21" s="16">
         <v>312864</v>
       </c>
-      <c r="F20" s="16">
-        <f>D20*E20</f>
+      <c r="G21" s="16">
+        <f>E21*F21</f>
         <v>8134464</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CAFETERÍA · CONTROLES ILUMINACIÓN</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.2.1</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de interruptor sencill, tubo eMT de 1/2", caja metálica tipo radwell, cable de cobre No 12 AWG LSZH, conector tipo resorte o emplame autodesforre, accesorios y elemntos de fijación,</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D22" s="21">
-        <v>2</v>
-      </c>
-      <c r="E22" s="16">
-        <v>301516</v>
-      </c>
-      <c r="F22" s="16">
-        <f>D22*E22</f>
-        <v>603032</v>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal CAFETERÍA · SALIDAS ILUMINACIÓN</t>
+        </is>
+      </c>
+      <c r="G22" s="14">
+        <f>SUM(G21:G21)</f>
+        <v>8134464</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2,2,2</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de interruptor doble, tubo EMT de 1/2", caja metálica tipo Radwell, cable No 12 AWG LSZH, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación,  transporte, aseo diario.</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D23" s="21">
-        <v>1</v>
-      </c>
-      <c r="E23" s="16">
-        <v>309032</v>
-      </c>
-      <c r="F23" s="16">
-        <f>D23*E23</f>
-        <v>309032</v>
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. CAFETERÍA · CONTROLES ILUMINACIÓN</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">3.1</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.1</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de interruptor sencill, tubo eMT de 1/2", caja metálica tipo radwell, cable de cobre No 12 AWG LSZH, conector tipo resorte o emplame autodesforre, accesorios y elemntos de fijación,</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E24" s="21">
+        <v>2</v>
+      </c>
+      <c r="F24" s="16">
+        <v>301516</v>
+      </c>
+      <c r="G24" s="16">
+        <f>E24*F24</f>
+        <v>603032</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2,2,2</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de interruptor triple, tubo EMT de 1/2", caja metálica tipo Radwell, cable No 12 AWG LSZH, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación,  transporte, aseo diario.</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de interruptor doble, tubo EMT de 1/2", caja metálica tipo Radwell, cable No 12 AWG LSZH, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación,  transporte, aseo diario.</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D24" s="21">
-        <v>2</v>
-      </c>
-      <c r="E24" s="16">
-        <v>320460</v>
-      </c>
-      <c r="F24" s="16">
-        <f>D24*E24</f>
-        <v>640920</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CAFETERÍA · LUMINARIAS</t>
-        </is>
+      <c r="E25" s="21">
+        <v>1</v>
+      </c>
+      <c r="F25" s="16">
+        <v>309032</v>
+      </c>
+      <c r="G25" s="16">
+        <f>E25*F25</f>
+        <v>309032</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2,3,1</t>
+          <t xml:space="preserve">3.3</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luminaria LED 120x30 Cm 40 W Sylvania Ref. P28399-41, marco metálico pintura electrostática color blanco, accesotios, elementos de fijación y trasporte.</t>
+          <t xml:space="preserve">2,2,2</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Suministro e instalación de interruptor triple, tubo EMT de 1/2", caja metálica tipo Radwell, cable No 12 AWG LSZH, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación,  transporte, aseo diario.</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D26" s="21">
-        <v>8</v>
-      </c>
-      <c r="E26" s="16">
-        <v>153584</v>
+      <c r="E26" s="21">
+        <v>2</v>
       </c>
       <c r="F26" s="16">
-        <f>D26*E26</f>
-        <v>1228672</v>
+        <v>320460</v>
+      </c>
+      <c r="G26" s="16">
+        <f>E26*F26</f>
+        <v>640920</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2,3,3</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Luminaria LED 60x60 Cm 40 W Sylvania Ref. P27916, marco metálico pintura electrostática color blanco, accesotios, elementos de fijación y anclaje, trasporte.</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D27" s="21">
-        <v>16</v>
-      </c>
-      <c r="E27" s="16">
-        <v>131640</v>
-      </c>
-      <c r="F27" s="16">
-        <f>D27*E27</f>
-        <v>2106240</v>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal CAFETERÍA · CONTROLES ILUMINACIÓN</t>
+        </is>
+      </c>
+      <c r="G27" s="14">
+        <f>SUM(G24:G26)</f>
+        <v>1552984</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALÓN 200  SALÓN DE MÚSICA · RED FUERZA</t>
+          <t xml:space="preserve">4. CAFETERÍA · LUMINARIAS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">4.1</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,3,1</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luminaria LED 120x30 Cm 40 W Sylvania Ref. P28399-41, marco metálico pintura electrostática color blanco, accesotios, elementos de fijación y trasporte.</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E29" s="21">
+        <v>8</v>
+      </c>
+      <c r="F29" s="16">
+        <v>153584</v>
+      </c>
+      <c r="G29" s="16">
+        <f>E29*F29</f>
+        <v>1228672</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,3,3</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luminaria LED 60x60 Cm 40 W Sylvania Ref. P27916, marco metálico pintura electrostática color blanco, accesotios, elementos de fijación y anclaje, trasporte.</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E30" s="21">
+        <v>16</v>
+      </c>
+      <c r="F30" s="16">
+        <v>131640</v>
+      </c>
+      <c r="G30" s="16">
+        <f>E30*F30</f>
+        <v>2106240</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal CAFETERÍA · LUMINARIAS</t>
+        </is>
+      </c>
+      <c r="G31" s="14">
+        <f>SUM(G29:G30)</f>
+        <v>3334912</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. SALÓN 200  SALÓN DE MÚSICA · RED FUERZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.1</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">1.1</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Suministro e instalación de tomacoriente monofásica normal de 15 A 120 V en canaleta metálica. Incluye: troquel metálico para toma eléctrica, cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje,
 transporte, marquilla de identificación y aseo diario.</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D29" s="21">
+      <c r="E33" s="21">
         <v>9</v>
       </c>
-      <c r="E29" s="16">
+      <c r="F33" s="16">
         <v>320488</v>
       </c>
-      <c r="F29" s="16">
-        <f>D29*E29</f>
+      <c r="G33" s="16">
+        <f>E33*F33</f>
         <v>2884392</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.2</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de canaleta metalica calibre 20-22 con división, pintura electrostática de 15x5 cm, color blanca.</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D30" s="21">
-        <v>26</v>
-      </c>
-      <c r="E30" s="16">
-        <v>74596</v>
-      </c>
-      <c r="F30" s="16">
-        <f>D30*E30</f>
-        <v>1939496</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.3</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de cable de cobre 3x12 trenzado AWG  LSZH azul</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D31" s="21">
-        <v>41</v>
-      </c>
-      <c r="E31" s="16">
-        <v>30172</v>
-      </c>
-      <c r="F31" s="16">
-        <f>D31*E31</f>
-        <v>1237052</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de cable de cobre No 12 AWG LSZH</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D32" s="21">
-        <v>273</v>
-      </c>
-      <c r="E32" s="16">
-        <v>17552</v>
-      </c>
-      <c r="F32" s="16">
-        <f>D32*E32</f>
-        <v>4791696</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de alambre de cobre desnudo No 14 AWG</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D33" s="21">
-        <v>157</v>
-      </c>
-      <c r="E33" s="16">
-        <v>14928</v>
-      </c>
-      <c r="F33" s="16">
-        <f>D33*E33</f>
-        <v>2343696</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6</t>
+          <t xml:space="preserve">5.2</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación de breaker tipo industrial de 3x40 A.</t>
+          <t xml:space="preserve">1.2</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D34" s="21">
-        <v>1</v>
-      </c>
-      <c r="E34" s="16">
-        <v>81852</v>
+          <t xml:space="preserve">Suministro e instalación de canaleta metalica calibre 20-22 con división, pintura electrostática de 15x5 cm, color blanca.</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E34" s="21">
+        <v>26</v>
       </c>
       <c r="F34" s="16">
-        <f>D34*E34</f>
-        <v>81852</v>
+        <v>74596</v>
+      </c>
+      <c r="G34" s="16">
+        <f>E34*F34</f>
+        <v>1939496</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.7</t>
+          <t xml:space="preserve">5.3</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación de breaker tipo enchufable de 3x20 A.</t>
+          <t xml:space="preserve">1.3</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D35" s="21">
-        <v>2</v>
-      </c>
-      <c r="E35" s="16">
-        <v>55152</v>
+          <t xml:space="preserve">Suministro e instalación de cable de cobre 3x12 trenzado AWG  LSZH azul</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E35" s="21">
+        <v>41</v>
       </c>
       <c r="F35" s="16">
-        <f>D35*E35</f>
-        <v>110304</v>
+        <v>30172</v>
+      </c>
+      <c r="G35" s="16">
+        <f>E35*F35</f>
+        <v>1237052</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.8</t>
+          <t xml:space="preserve">5.4</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación de breaker tipo enchufable de 1x20 A.</t>
+          <t xml:space="preserve">1.4</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D36" s="21">
-        <v>5</v>
-      </c>
-      <c r="E36" s="16">
-        <v>41688</v>
+          <t xml:space="preserve">Suministro e instalación de cable de cobre No 12 AWG LSZH</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E36" s="21">
+        <v>273</v>
       </c>
       <c r="F36" s="16">
-        <f>D36*E36</f>
-        <v>208440</v>
+        <v>17552</v>
+      </c>
+      <c r="G36" s="16">
+        <f>E36*F36</f>
+        <v>4791696</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.9</t>
+          <t xml:space="preserve">5.5</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación de breaker tipo riel de 3x40 A.</t>
+          <t xml:space="preserve">1.5</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D37" s="21">
-        <v>1</v>
-      </c>
-      <c r="E37" s="16">
-        <v>81852</v>
+          <t xml:space="preserve">Suministro e instalación de alambre de cobre desnudo No 14 AWG</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E37" s="21">
+        <v>157</v>
       </c>
       <c r="F37" s="16">
-        <f>D37*E37</f>
-        <v>81852</v>
+        <v>14928</v>
+      </c>
+      <c r="G37" s="16">
+        <f>E37*F37</f>
+        <v>2343696</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.10</t>
+          <t xml:space="preserve">5.6</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro de tablero metálico trifásico de 18 circuitos con espacio para totalizador</t>
+          <t xml:space="preserve">1.6</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Suministro e instalación de breaker tipo industrial de 3x40 A.</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D38" s="21">
+      <c r="E38" s="21">
         <v>1</v>
       </c>
-      <c r="E38" s="16">
-        <v>3129564</v>
-      </c>
       <c r="F38" s="16">
-        <f>D38*E38</f>
-        <v>3129564</v>
+        <v>81852</v>
+      </c>
+      <c r="G38" s="16">
+        <f>E38*F38</f>
+        <v>81852</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.11</t>
+          <t xml:space="preserve">5.7</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación de caja de paso metálica de 30*30*20 Cm, elementos de fijación y anclaje.</t>
+          <t xml:space="preserve">1.7</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Suministro e instalación de breaker tipo enchufable de 3x20 A.</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D39" s="21">
-        <v>5</v>
-      </c>
-      <c r="E39" s="16">
-        <v>88536</v>
+      <c r="E39" s="21">
+        <v>2</v>
       </c>
       <c r="F39" s="16">
-        <f>D39*E39</f>
-        <v>442680</v>
+        <v>55152</v>
+      </c>
+      <c r="G39" s="16">
+        <f>E39*F39</f>
+        <v>110304</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.12</t>
+          <t xml:space="preserve">5.8</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reemplazo tubería sobrepuesta PVC existente de 2" en costado occidental por tubería EMT de 2", incluye unionesy terminales en EMT 2"</t>
+          <t xml:space="preserve">1.8</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D40" s="21">
-        <v>27</v>
-      </c>
-      <c r="E40" s="16">
-        <v>133824</v>
+          <t xml:space="preserve">Suministro e instalación de breaker tipo enchufable de 1x20 A.</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E40" s="21">
+        <v>5</v>
       </c>
       <c r="F40" s="16">
-        <f>D40*E40</f>
-        <v>3613248</v>
+        <v>41688</v>
+      </c>
+      <c r="G40" s="16">
+        <f>E40*F40</f>
+        <v>208440</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.13</t>
+          <t xml:space="preserve">5.9</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instalación tubería sobrepuesta de 1 1/2" entre caja de paso existente y caja de paso nueva, incluye uniones y terminales en EMT 1 1/2"</t>
+          <t xml:space="preserve">1.9</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D41" s="21">
-        <v>27</v>
-      </c>
-      <c r="E41" s="16">
-        <v>114616</v>
+          <t xml:space="preserve">Suministro e instalación de breaker tipo riel de 3x40 A.</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E41" s="21">
+        <v>1</v>
       </c>
       <c r="F41" s="16">
-        <f>D41*E41</f>
-        <v>3094632</v>
+        <v>81852</v>
+      </c>
+      <c r="G41" s="16">
+        <f>E41*F41</f>
+        <v>81852</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.14</t>
+          <t xml:space="preserve">5.10</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regata en muro tubería de 1 1/2"</t>
+          <t xml:space="preserve">1.10</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D42" s="21">
-        <v>5</v>
-      </c>
-      <c r="E42" s="16">
-        <v>52956</v>
+          <t xml:space="preserve">Suministro de tablero metálico trifásico de 18 circuitos con espacio para totalizador</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E42" s="21">
+        <v>1</v>
       </c>
       <c r="F42" s="16">
-        <f>D42*E42</f>
-        <v>264780</v>
+        <v>3129564</v>
+      </c>
+      <c r="G42" s="16">
+        <f>E42*F42</f>
+        <v>3129564</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.15</t>
+          <t xml:space="preserve">5.11</t>
         </is>
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regata en piso tubería de 1 1/2"</t>
+          <t xml:space="preserve">1.11</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D43" s="21">
-        <v>13</v>
-      </c>
-      <c r="E43" s="16">
-        <v>57040</v>
+          <t xml:space="preserve">Suministro e instalación de caja de paso metálica de 30*30*20 Cm, elementos de fijación y anclaje.</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E43" s="21">
+        <v>5</v>
       </c>
       <c r="F43" s="16">
-        <f>D43*E43</f>
-        <v>741520</v>
+        <v>88536</v>
+      </c>
+      <c r="G43" s="16">
+        <f>E43*F43</f>
+        <v>442680</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.16</t>
+          <t xml:space="preserve">5.12</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acometida entre Tablero principal y Tablero Eléctrico Sala de Música en cable de cobre No 6 AWG LSZH. 3 fases y neutro</t>
+          <t xml:space="preserve">1.12</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Reemplazo tubería sobrepuesta PVC existente de 2" en costado occidental por tubería EMT de 2", incluye unionesy terminales en EMT 2"</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">ML</t>
         </is>
       </c>
-      <c r="D44" s="21">
-        <v>240</v>
-      </c>
-      <c r="E44" s="16">
-        <v>47044</v>
+      <c r="E44" s="21">
+        <v>27</v>
       </c>
       <c r="F44" s="16">
-        <f>D44*E44</f>
-        <v>11290560</v>
+        <v>133824</v>
+      </c>
+      <c r="G44" s="16">
+        <f>E44*F44</f>
+        <v>3613248</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.17</t>
+          <t xml:space="preserve">5.13</t>
         </is>
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acometida entre Tablero principal y Tablero Eléctrico Sala de Música en cable de cobre No 10 AWG LSZH. Tierra</t>
+          <t xml:space="preserve">1.13</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Instalación tubería sobrepuesta de 1 1/2" entre caja de paso existente y caja de paso nueva, incluye uniones y terminales en EMT 1 1/2"</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">ML</t>
         </is>
       </c>
-      <c r="D45" s="21">
-        <v>60</v>
-      </c>
-      <c r="E45" s="16">
-        <v>36656</v>
+      <c r="E45" s="21">
+        <v>27</v>
       </c>
       <c r="F45" s="16">
-        <f>D45*E45</f>
-        <v>2199360</v>
+        <v>114616</v>
+      </c>
+      <c r="G45" s="16">
+        <f>E45*F45</f>
+        <v>3094632</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.18</t>
+          <t xml:space="preserve">5.14</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desalambrado y realambrado de acometida existente por cambio de tubería.</t>
+          <t xml:space="preserve">1.14</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBL</t>
-        </is>
-      </c>
-      <c r="D46" s="21">
-        <v>1</v>
-      </c>
-      <c r="E46" s="16">
-        <v>2712980</v>
+          <t xml:space="preserve">Regata en muro tubería de 1 1/2"</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E46" s="21">
+        <v>5</v>
       </c>
       <c r="F46" s="16">
-        <f>D46*E46</f>
-        <v>2712980</v>
+        <v>52956</v>
+      </c>
+      <c r="G46" s="16">
+        <f>E46*F46</f>
+        <v>264780</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SALÓN 200  SALÓN DE MÚSICA · SALIDAS ILUMINACIÓN</t>
-        </is>
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.15</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.15</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regata en piso tubería de 1 1/2"</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E47" s="21">
+        <v>13</v>
+      </c>
+      <c r="F47" s="16">
+        <v>57040</v>
+      </c>
+      <c r="G47" s="16">
+        <f>E47*F47</f>
+        <v>741520</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2,1,1</t>
+          <t xml:space="preserve">5.16</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
+          <t xml:space="preserve">1.16</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D48" s="21">
-        <v>24</v>
-      </c>
-      <c r="E48" s="16">
-        <v>312864</v>
+          <t xml:space="preserve">Acometida entre Tablero principal y Tablero Eléctrico Sala de Música en cable de cobre No 6 AWG LSZH. 3 fases y neutro</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E48" s="21">
+        <v>240</v>
       </c>
       <c r="F48" s="16">
-        <f>D48*E48</f>
-        <v>7508736</v>
+        <v>47044</v>
+      </c>
+      <c r="G48" s="16">
+        <f>E48*F48</f>
+        <v>11290560</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SALÓN 200  SALÓN DE MÚSICA · CONTROLES ILUMINACIÓN</t>
-        </is>
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.17</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.17</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acometida entre Tablero principal y Tablero Eléctrico Sala de Música en cable de cobre No 10 AWG LSZH. Tierra</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E49" s="21">
+        <v>60</v>
+      </c>
+      <c r="F49" s="16">
+        <v>36656</v>
+      </c>
+      <c r="G49" s="16">
+        <f>E49*F49</f>
+        <v>2199360</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2,2,2</t>
+          <t xml:space="preserve">5.18</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación de interruptor triple, tubo EMT de 3/4", caja metálica tipo Radwell, cable No 12 aWG LSZH, conector tipo resorte o empalme autodesforre, transporte, aseo diario.</t>
+          <t xml:space="preserve">1.18</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Desalambrado y realambrado de acometida existente por cambio de tubería.</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GBL</t>
+        </is>
+      </c>
+      <c r="E50" s="21">
+        <v>1</v>
+      </c>
+      <c r="F50" s="16">
+        <v>2712980</v>
+      </c>
+      <c r="G50" s="16">
+        <f>E50*F50</f>
+        <v>2712980</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal SALÓN 200  SALÓN DE MÚSICA · RED FUERZA</t>
+        </is>
+      </c>
+      <c r="G51" s="14">
+        <f>SUM(G33:G50)</f>
+        <v>41168104</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. SALÓN 200  SALÓN DE MÚSICA · SALIDAS ILUMINACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,1,1</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D50" s="21">
-        <v>1</v>
-      </c>
-      <c r="E50" s="16">
-        <v>320460</v>
-      </c>
-      <c r="F50" s="16">
-        <f>D50*E50</f>
-        <v>320460</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SALÓN 200  SALÓN DE MÚSICA · LUMINARIAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2,3,1</t>
-        </is>
-      </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDIENTE-POSIBLE USO DE RIEL Y LUMINARIA SYLVANIA   ⛔ SIN PRECIO: no suma al total</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D52" s="19">
+      <c r="E53" s="21">
         <v>24</v>
       </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CASETA AIRE ACONDICIONADO · RED FUERZA</t>
-        </is>
+      <c r="F53" s="16">
+        <v>312864</v>
+      </c>
+      <c r="G53" s="16">
+        <f>E53*F53</f>
+        <v>7508736</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.1</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de tomacoriente monofásica de 15 A 120 V, en muro, tubo PVC 1", tubo PVC 1/2", caja metálica Ref. 5800,  cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje, transporte,  marquilla de identificación y aseo diario.</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D54" s="21">
-        <v>1</v>
-      </c>
-      <c r="E54" s="16">
-        <v>613836</v>
-      </c>
-      <c r="F54" s="16">
-        <f>D54*E54</f>
-        <v>613836</v>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal SALÓN 200  SALÓN DE MÚSICA · SALIDAS ILUMINACIÓN</t>
+        </is>
+      </c>
+      <c r="G54" s="14">
+        <f>SUM(G53:G53)</f>
+        <v>7508736</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASETA AIRE ACONDICIONADO · SALIDAS ILUMINACIÓN</t>
+          <t xml:space="preserve">7. SALÓN 200  SALÓN DE MÚSICA · CONTROLES ILUMINACIÓN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">7.1</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,2,2</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de interruptor triple, tubo EMT de 3/4", caja metálica tipo Radwell, cable No 12 aWG LSZH, conector tipo resorte o empalme autodesforre, transporte, aseo diario.</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E56" s="21">
+        <v>1</v>
+      </c>
+      <c r="F56" s="16">
+        <v>320460</v>
+      </c>
+      <c r="G56" s="16">
+        <f>E56*F56</f>
+        <v>320460</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal SALÓN 200  SALÓN DE MÚSICA · CONTROLES ILUMINACIÓN</t>
+        </is>
+      </c>
+      <c r="G57" s="14">
+        <f>SUM(G56:G56)</f>
+        <v>320460</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. SALÓN 200  SALÓN DE MÚSICA · LUMINARIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.1</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,3,1</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDIENTE-POSIBLE USO DE RIEL Y LUMINARIA SYLVANIA   ⛔ SIN PRECIO: no suma al total</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E59" s="19">
+        <v>24</v>
+      </c>
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. CASETA AIRE ACONDICIONADO · RED FUERZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.1</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de tomacoriente monofásica de 15 A 120 V, en muro, tubo PVC 1", tubo PVC 1/2", caja metálica Ref. 5800,  cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje, transporte,  marquilla de identificación y aseo diario.</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E61" s="21">
+        <v>1</v>
+      </c>
+      <c r="F61" s="16">
+        <v>613836</v>
+      </c>
+      <c r="G61" s="16">
+        <f>E61*F61</f>
+        <v>613836</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal CASETA AIRE ACONDICIONADO · RED FUERZA</t>
+        </is>
+      </c>
+      <c r="G62" s="14">
+        <f>SUM(G61:G61)</f>
+        <v>613836</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. CASETA AIRE ACONDICIONADO · SALIDAS ILUMINACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.1</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2,1,1</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
         </is>
       </c>
-      <c r="C56" s="15" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D56" s="21">
+      <c r="E64" s="21">
         <v>2</v>
       </c>
-      <c r="E56" s="16">
+      <c r="F64" s="16">
         <v>312864</v>
       </c>
-      <c r="F56" s="16">
-        <f>D56*E56</f>
+      <c r="G64" s="16">
+        <f>E64*F64</f>
         <v>625728</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CASETA AIRE ACONDICIONADO · CONTROLES ILUMINACIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="inlineStr">
+    <row r="65">
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal CASETA AIRE ACONDICIONADO · SALIDAS ILUMINACIÓN</t>
+        </is>
+      </c>
+      <c r="G65" s="14">
+        <f>SUM(G64:G64)</f>
+        <v>625728</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11. CASETA AIRE ACONDICIONADO · CONTROLES ILUMINACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.1</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">2.2.1</t>
         </is>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="C67" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Suministro e instalación de interruptor sencill, tubo eMT de 1/2", caja metálica tipo radwell, cable de cobre No 12 AWG LSZH, conector tipo resorte o emplame autodesforre, accesorios y elemntos de fijación,</t>
         </is>
       </c>
-      <c r="C58" s="15" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D58" s="21">
+      <c r="E67" s="21">
         <v>3</v>
       </c>
-      <c r="E58" s="16">
+      <c r="F67" s="16">
         <v>301516</v>
       </c>
-      <c r="F58" s="16">
-        <f>D58*E58</f>
+      <c r="G67" s="16">
+        <f>E67*F67</f>
         <v>904548</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CASETA AIRE ACONDICIONADO · LUMINARIAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+    <row r="68">
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal CASETA AIRE ACONDICIONADO · CONTROLES ILUMINACIÓN</t>
+        </is>
+      </c>
+      <c r="G68" s="14">
+        <f>SUM(G67:G67)</f>
+        <v>904548</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12. CASETA AIRE ACONDICIONADO · LUMINARIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.1</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">2,3,3</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Luminaria LED 60x60 Cm 40 W Sylvania Ref. P27916, marco metálico pintura electrostática color blanco, accesotios, elementos de fijación y trasporte.</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="D70" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D60" s="21">
+      <c r="E70" s="21">
         <v>1</v>
       </c>
-      <c r="E60" s="16">
+      <c r="F70" s="16">
         <v>131640</v>
       </c>
-      <c r="F60" s="16">
-        <f>D60*E60</f>
+      <c r="G70" s="16">
+        <f>E70*F70</f>
         <v>131640</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SALÓN 216  SALA DE INSTRUMENTOS · RED FUERZA</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+    <row r="71">
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal CASETA AIRE ACONDICIONADO · LUMINARIAS</t>
+        </is>
+      </c>
+      <c r="G71" s="14">
+        <f>SUM(G70:G70)</f>
+        <v>131640</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13. SALÓN 216  SALA DE INSTRUMENTOS · RED FUERZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.1</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">1.1</t>
         </is>
       </c>
-      <c r="B62" s="15" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Suministro e instalación de tomacoriente monofásica normal de 15 A 120 V en canaleta metálica. Incluye: troquel metálico para toma eléctrica, cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje,
 transporte, marquilla de identificación y aseo diario.</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="D73" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D62" s="21">
+      <c r="E73" s="21">
         <v>13</v>
       </c>
-      <c r="E62" s="16">
+      <c r="F73" s="16">
         <v>320488</v>
       </c>
-      <c r="F62" s="16">
-        <f>D62*E62</f>
+      <c r="G73" s="16">
+        <f>E73*F73</f>
         <v>4166344</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.2</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">1.2</t>
         </is>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="C74" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Suministro e instalación de canaleta metalica calibre 20-22 con división, pintura electrostática de 15x5 cm, color blanca.</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="D74" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">ML</t>
         </is>
       </c>
-      <c r="D63" s="21">
+      <c r="E74" s="21">
         <v>30</v>
       </c>
-      <c r="E63" s="16">
+      <c r="F74" s="16">
         <v>74596</v>
       </c>
-      <c r="F63" s="16">
-        <f>D63*E63</f>
+      <c r="G74" s="16">
+        <f>E74*F74</f>
         <v>2237880</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.3</t>
-        </is>
-      </c>
-      <c r="B64" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de cable de cobre 3x12 trenzado AWG  LSZH azul</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D64" s="21">
-        <v>63</v>
-      </c>
-      <c r="E64" s="16">
-        <v>30172</v>
-      </c>
-      <c r="F64" s="16">
-        <f>D64*E64</f>
-        <v>1900836</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de cable de cobre No 12 AWG LSZH</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D65" s="21">
-        <v>273</v>
-      </c>
-      <c r="E65" s="16">
-        <v>17552</v>
-      </c>
-      <c r="F65" s="16">
-        <f>D65*E65</f>
-        <v>4791696</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5</t>
-        </is>
-      </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de alambre de cobre desnudo No 14 AWG</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ML</t>
-        </is>
-      </c>
-      <c r="D66" s="21">
-        <v>79</v>
-      </c>
-      <c r="E66" s="16">
-        <v>14928</v>
-      </c>
-      <c r="F66" s="16">
-        <f>D66*E66</f>
-        <v>1179312</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.6</t>
-        </is>
-      </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de breaker tipo enchufable de 1x20 A.</t>
-        </is>
-      </c>
-      <c r="C67" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D67" s="21">
-        <v>3</v>
-      </c>
-      <c r="E67" s="16">
-        <v>41688</v>
-      </c>
-      <c r="F67" s="16">
-        <f>D67*E67</f>
-        <v>125064</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.7</t>
-        </is>
-      </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Desconexión, deslambrado  de acometida existente para cambio tablero existente.</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GBL</t>
-        </is>
-      </c>
-      <c r="D68" s="21">
-        <v>1</v>
-      </c>
-      <c r="E68" s="16">
-        <v>1929244</v>
-      </c>
-      <c r="F68" s="16">
-        <f>D68*E68</f>
-        <v>1929244</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.8</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Alambrado, traslado y reconexión de red eléctrica existente a nuevo tablero eléctrico.</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GBL</t>
-        </is>
-      </c>
-      <c r="D69" s="21">
-        <v>1</v>
-      </c>
-      <c r="E69" s="16">
-        <v>3259128</v>
-      </c>
-      <c r="F69" s="16">
-        <f>D69*E69</f>
-        <v>3259128</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SALÓN 216  SALA DE INSTRUMENTOS · SALIDAS ILUMINACIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2,1,1</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D71" s="21">
-        <v>9</v>
-      </c>
-      <c r="E71" s="16">
-        <v>312864</v>
-      </c>
-      <c r="F71" s="16">
-        <f>D71*E71</f>
-        <v>2815776</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SALÓN 216  SALA DE INSTRUMENTOS · CONTROLES ILUMINACIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2,2,2</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suministro e instalación de interruptor triple, tubo EMT de 3/4", caja metálica tipo Radwell, cable No 12 aWG LSZH, conector tipo resorte o empalme autodesforre, transporte, aseo diario.</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UND</t>
-        </is>
-      </c>
-      <c r="D73" s="21">
-        <v>1</v>
-      </c>
-      <c r="E73" s="16">
-        <v>320460</v>
-      </c>
-      <c r="F73" s="16">
-        <f>D73*E73</f>
-        <v>320460</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SALÓN 216  SALA DE INSTRUMENTOS · LUMINARIAS</t>
-        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">13.3</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de cable de cobre 3x12 trenzado AWG  LSZH azul</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E75" s="21">
+        <v>63</v>
+      </c>
+      <c r="F75" s="16">
+        <v>30172</v>
+      </c>
+      <c r="G75" s="16">
+        <f>E75*F75</f>
+        <v>1900836</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.4</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de cable de cobre No 12 AWG LSZH</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E76" s="21">
+        <v>273</v>
+      </c>
+      <c r="F76" s="16">
+        <v>17552</v>
+      </c>
+      <c r="G76" s="16">
+        <f>E76*F76</f>
+        <v>4791696</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.5</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de alambre de cobre desnudo No 14 AWG</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML</t>
+        </is>
+      </c>
+      <c r="E77" s="21">
+        <v>79</v>
+      </c>
+      <c r="F77" s="16">
+        <v>14928</v>
+      </c>
+      <c r="G77" s="16">
+        <f>E77*F77</f>
+        <v>1179312</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.6</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.6</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de breaker tipo enchufable de 1x20 A.</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E78" s="21">
+        <v>3</v>
+      </c>
+      <c r="F78" s="16">
+        <v>41688</v>
+      </c>
+      <c r="G78" s="16">
+        <f>E78*F78</f>
+        <v>125064</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.7</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.7</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Desconexión, deslambrado  de acometida existente para cambio tablero existente.</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GBL</t>
+        </is>
+      </c>
+      <c r="E79" s="21">
+        <v>1</v>
+      </c>
+      <c r="F79" s="16">
+        <v>1929244</v>
+      </c>
+      <c r="G79" s="16">
+        <f>E79*F79</f>
+        <v>1929244</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13.8</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.8</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alambrado, traslado y reconexión de red eléctrica existente a nuevo tablero eléctrico.</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GBL</t>
+        </is>
+      </c>
+      <c r="E80" s="21">
+        <v>1</v>
+      </c>
+      <c r="F80" s="16">
+        <v>3259128</v>
+      </c>
+      <c r="G80" s="16">
+        <f>E80*F80</f>
+        <v>3259128</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal SALÓN 216  SALA DE INSTRUMENTOS · RED FUERZA</t>
+        </is>
+      </c>
+      <c r="G81" s="14">
+        <f>SUM(G73:G80)</f>
+        <v>19589504</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14. SALÓN 216  SALA DE INSTRUMENTOS · SALIDAS ILUMINACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14.1</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,1,1</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E83" s="21">
+        <v>9</v>
+      </c>
+      <c r="F83" s="16">
+        <v>312864</v>
+      </c>
+      <c r="G83" s="16">
+        <f>E83*F83</f>
+        <v>2815776</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal SALÓN 216  SALA DE INSTRUMENTOS · SALIDAS ILUMINACIÓN</t>
+        </is>
+      </c>
+      <c r="G84" s="14">
+        <f>SUM(G83:G83)</f>
+        <v>2815776</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15. SALÓN 216  SALA DE INSTRUMENTOS · CONTROLES ILUMINACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.1</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,2,2</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suministro e instalación de interruptor triple, tubo EMT de 3/4", caja metálica tipo Radwell, cable No 12 aWG LSZH, conector tipo resorte o empalme autodesforre, transporte, aseo diario.</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UND</t>
+        </is>
+      </c>
+      <c r="E86" s="21">
+        <v>1</v>
+      </c>
+      <c r="F86" s="16">
+        <v>320460</v>
+      </c>
+      <c r="G86" s="16">
+        <f>E86*F86</f>
+        <v>320460</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal SALÓN 216  SALA DE INSTRUMENTOS · CONTROLES ILUMINACIÓN</t>
+        </is>
+      </c>
+      <c r="G87" s="14">
+        <f>SUM(G86:G86)</f>
+        <v>320460</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16. SALÓN 216  SALA DE INSTRUMENTOS · LUMINARIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.1</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2,3,1</t>
         </is>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="C89" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Luminaria panel LED 120*30 Cm Sylvania Ref. P27916-41</t>
         </is>
       </c>
-      <c r="C75" s="15" t="inlineStr">
+      <c r="D89" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">UND</t>
         </is>
       </c>
-      <c r="D75" s="21">
+      <c r="E89" s="21">
         <v>9</v>
       </c>
-      <c r="E75" s="16">
+      <c r="F89" s="16">
         <v>153584</v>
       </c>
-      <c r="F75" s="16">
-        <f>D75*E75</f>
+      <c r="G89" s="16">
+        <f>E89*F89</f>
         <v>1382256</v>
       </c>
     </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="D77" s="13" t="inlineStr">
+    <row r="90">
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal SALÓN 216  SALA DE INSTRUMENTOS · LUMINARIAS</t>
+        </is>
+      </c>
+      <c r="G90" s="14">
+        <f>SUM(G89:G89)</f>
+        <v>1382256</v>
+      </c>
+    </row>
+    <row r="91"/>
+    <row r="92">
+      <c r="C92" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">COSTOS DIRECTOS</t>
         </is>
       </c>
-      <c r="F77" s="14">
-        <f>SUM(F7:F75)</f>
+      <c r="G92" s="14">
+        <f>SUM(G19,G22,G27,G31,G51,G54,G57,G62,G65,G68,G71,G81,G84,G87,G90)</f>
         <v>111614712</v>
       </c>
     </row>
-    <row r="78">
-      <c r="D78" s="11" t="inlineStr">
+    <row r="93">
+      <c r="C93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Administración (A) — 19.17 %</t>
         </is>
       </c>
-      <c r="F78" s="12">
-        <f>F77*0.1917</f>
+      <c r="G93" s="12">
+        <f>G92*0.1917</f>
         <v>21396540.29</v>
       </c>
     </row>
-    <row r="79">
-      <c r="D79" s="11" t="inlineStr">
+    <row r="94">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Imprevistos (I) — 1.5 %</t>
         </is>
       </c>
-      <c r="F79" s="12">
-        <f>F77*0.015</f>
+      <c r="G94" s="12">
+        <f>G92*0.015</f>
         <v>1674220.68</v>
       </c>
     </row>
-    <row r="80">
-      <c r="D80" s="11" t="inlineStr">
+    <row r="95">
+      <c r="C95" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Utilidad (U) — 5.33 %</t>
         </is>
       </c>
-      <c r="F80" s="12">
-        <f>F77*0.0533</f>
+      <c r="G95" s="12">
+        <f>G92*0.0533</f>
         <v>5949064.15</v>
       </c>
     </row>
-    <row r="81">
-      <c r="D81" s="11" t="inlineStr">
+    <row r="96">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">IVA sobre la utilidad (19 %)</t>
         </is>
       </c>
-      <c r="F81" s="12">
-        <f>F80*0.19</f>
+      <c r="G96" s="12">
+        <f>G95*0.19</f>
         <v>1130322.19</v>
       </c>
     </row>
-    <row r="82">
-      <c r="D82" s="13" t="inlineStr">
+    <row r="97">
+      <c r="C97" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">COSTOS INDIRECTOS</t>
         </is>
       </c>
-      <c r="F82" s="14">
-        <f>SUM(F78:F81)</f>
+      <c r="G97" s="14">
+        <f>SUM(G93:G96)</f>
         <v>30150147.310000006</v>
       </c>
     </row>
-    <row r="83">
-      <c r="D83" s="15" t="inlineStr">
+    <row r="98">
+      <c r="C98" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">TOTAL</t>
         </is>
       </c>
-      <c r="F83" s="16">
-        <f>ROUND(F77+F82,0)</f>
+      <c r="G98" s="16">
+        <f>ROUND(G92+G97,0)</f>
         <v>141764859</v>
       </c>
     </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Elaboró:</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Revisó:</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Aprobó:</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88">
-      <c r="A88" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leyenda: fila SIN COLOR = precio de un contrato adjudicado (Nogal 4, 2025) servido en su misma región. Fila AMARILLA = precio con APU pero derivado por factor regional o estimado: no está verificado y requiere cotización. Fila ÁMBAR = precio del archivo importado o tecleado a mano, sin APU de respaldo en el catálogo (suma al total y queda declarado). Fila ROJA = ítem sin precio: NO suma al total — un $0 sería un precio inventado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="17" t="inlineStr">
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leyenda: fila SIN COLOR = precio de un contrato adjudicado (Nogal 4, 2025) servido en su misma región, o insumos con cotización de proveedor cargada. Fila AMARILLA = precio con APU pero derivado por factor regional o estimado: no está verificado y requiere cotización. Fila ÁMBAR = precio del archivo importado o tecleado a mano, sin APU de respaldo en el catálogo (suma al total y queda declarado). Fila ROJA = ítem sin precio: NO suma al total — un $0 sería un precio inventado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha de generación: Base de precios: Presupuesto Nogal 4 · contrato adjudicado 2025 (Bogotá). Región de precios: Bogotá / Sabana. Factor prestacional aplicado sobre el jornal: 1.55. Catálogo 2.0.0, base de precios 2026-08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Precios de REFERENCIA regionalizada, no cotizaciones. Este presupuesto es una AYUDA DE LECTURA para decidir a qué presentarse, no una oferta: verifique contra cotización real antes de presentar.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="17" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1 ítem(s) no se pudieron costear y NO suman al total. Se listan con su motivo: un ítem sin precio vale «sin dato», nunca cero.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="17" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">53 ítem(s) llevan precio del archivo importado o tecleado a mano, SIN composición de APU que lo respalde: suman al total pero no al reparto por componente, y en el Excel salen marcados.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="17" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">El catálogo de precios NO está cargado en Redis: se usó la semilla del repositorio. Cárguelo desde /admin.html para trabajar con la versión vigente.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="17" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">El margen NO descuenta la contribución especial de obra pública (5 % del valor del contrato, Ley 418/1997) ni las estampillas. Sobre este precio la contribución sola serían 7.031.726,86 COP. Cárguelas en «deducciones de acta (%)» para ver el margen real.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="17" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticipo sin dato: la financiación requerida se calculó como si NO hubiera anticipo, que es el escenario conservador.</t>
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• AIU fuera de la banda típica: Imprevistos (I) en 1.5 % (banda típica 3–5 %). Las bandas del cap. 11 del Manual del Analista son INDICATIVAS, no una regla: el AIU real del contrato Nogal 4 (adjudicado) fue 19,17 / 1,50 / 5,33, con su «I» por debajo de la banda. Verifique que el pliego no fije el AIU y que la oferta lo pueda sostener.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Hay ítems sin precio: 1 de 54 ítem(s) (1.85 %) no tienen precio: no suman al total y en el Excel salen en ROJO con las celdas de valor VACÍAS. El porcentaje es de ÍTEMS, no de dinero: cuánto valen es justamente lo que no se sabe, así que el total de abajo es una COTA INFERIOR del presupuesto real.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A93:F93"/>
-    <mergeCell ref="A94:F94"/>
+  <mergeCells count="51">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="C84:F84"/>
+    <mergeCell ref="A85:G85"/>
+    <mergeCell ref="C87:F87"/>
+    <mergeCell ref="A88:G88"/>
+    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="C92:F92"/>
+    <mergeCell ref="C93:F93"/>
+    <mergeCell ref="C94:F94"/>
+    <mergeCell ref="C95:F95"/>
+    <mergeCell ref="C96:F96"/>
+    <mergeCell ref="C97:F97"/>
+    <mergeCell ref="C98:F98"/>
+    <mergeCell ref="A103:G103"/>
+    <mergeCell ref="A104:G104"/>
+    <mergeCell ref="A105:G105"/>
+    <mergeCell ref="A106:G106"/>
+    <mergeCell ref="A107:G107"/>
+    <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A109:G109"/>
+    <mergeCell ref="A110:G110"/>
+    <mergeCell ref="A111:G111"/>
+    <mergeCell ref="A112:G112"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
@@ -2057,6 +2544,8 @@
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3889,36 +4378,68 @@
       </c>
     </row>
     <row r="209"/>
+    <row r="210"/>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analizó y elaboró los APU:</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Firma:</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nombre / Matrícula profesional:</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Los factores de cada línea (cantidad base, desperdicio, rendimiento, distancia y recargo prestacional) van en las columnas F y G para que el análisis se pueda auditar sin leer la descripción.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="154">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+  <mergeCells count="159">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A6:G6"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A26:G26"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A42:D42"/>
@@ -3927,49 +4448,49 @@
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A54:G54"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A58:G58"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A62:G62"/>
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A66:G66"/>
     <mergeCell ref="A68:D68"/>
     <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A70:G70"/>
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A76:D76"/>
     <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A78:G78"/>
     <mergeCell ref="A80:D80"/>
     <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A82:G82"/>
     <mergeCell ref="A84:D84"/>
     <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A86:G86"/>
     <mergeCell ref="A88:D88"/>
     <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A90:G90"/>
     <mergeCell ref="A92:D92"/>
     <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A94:G94"/>
     <mergeCell ref="A96:D96"/>
     <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A98:G98"/>
     <mergeCell ref="A100:D100"/>
     <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A102:G102"/>
     <mergeCell ref="A104:D104"/>
     <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A106:G106"/>
     <mergeCell ref="A108:D108"/>
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="A111:D111"/>
@@ -3978,73 +4499,78 @@
     <mergeCell ref="A115:C115"/>
     <mergeCell ref="A117:D117"/>
     <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A119:G119"/>
     <mergeCell ref="A121:D121"/>
     <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A123:G123"/>
     <mergeCell ref="A125:D125"/>
     <mergeCell ref="A126:C126"/>
-    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A127:G127"/>
     <mergeCell ref="A129:D129"/>
     <mergeCell ref="A130:C130"/>
-    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A131:G131"/>
     <mergeCell ref="A133:D133"/>
     <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A135:G135"/>
     <mergeCell ref="A137:D137"/>
     <mergeCell ref="A138:C138"/>
     <mergeCell ref="A140:D140"/>
     <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A142:G142"/>
     <mergeCell ref="A144:D144"/>
     <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A146:G146"/>
     <mergeCell ref="A148:D148"/>
-    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="A149:G149"/>
     <mergeCell ref="A151:D151"/>
     <mergeCell ref="A152:C152"/>
-    <mergeCell ref="A153:E153"/>
+    <mergeCell ref="A153:G153"/>
     <mergeCell ref="A155:D155"/>
     <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A157:E157"/>
+    <mergeCell ref="A157:G157"/>
     <mergeCell ref="A159:D159"/>
     <mergeCell ref="A160:C160"/>
-    <mergeCell ref="A161:E161"/>
+    <mergeCell ref="A161:G161"/>
     <mergeCell ref="A163:D163"/>
     <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:E165"/>
+    <mergeCell ref="A165:G165"/>
     <mergeCell ref="A167:D167"/>
     <mergeCell ref="A168:C168"/>
-    <mergeCell ref="A169:E169"/>
+    <mergeCell ref="A169:G169"/>
     <mergeCell ref="A171:D171"/>
     <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:E173"/>
+    <mergeCell ref="A173:G173"/>
     <mergeCell ref="A175:D175"/>
     <mergeCell ref="A176:C176"/>
-    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A177:G177"/>
     <mergeCell ref="A179:D179"/>
     <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:E181"/>
+    <mergeCell ref="A181:G181"/>
     <mergeCell ref="A183:D183"/>
     <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A185:E185"/>
+    <mergeCell ref="A185:G185"/>
     <mergeCell ref="A187:D187"/>
     <mergeCell ref="A188:C188"/>
-    <mergeCell ref="A189:E189"/>
+    <mergeCell ref="A189:G189"/>
     <mergeCell ref="A191:D191"/>
     <mergeCell ref="A192:C192"/>
-    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A193:G193"/>
     <mergeCell ref="A195:D195"/>
     <mergeCell ref="A196:C196"/>
     <mergeCell ref="A198:D198"/>
     <mergeCell ref="A199:C199"/>
-    <mergeCell ref="A200:E200"/>
+    <mergeCell ref="A200:G200"/>
     <mergeCell ref="A202:D202"/>
     <mergeCell ref="A203:C203"/>
-    <mergeCell ref="A204:E204"/>
+    <mergeCell ref="A204:G204"/>
     <mergeCell ref="A206:D206"/>
     <mergeCell ref="A207:C207"/>
-    <mergeCell ref="A208:E208"/>
+    <mergeCell ref="A208:G208"/>
+    <mergeCell ref="A211:C211"/>
+    <mergeCell ref="D211:G211"/>
+    <mergeCell ref="A212:C212"/>
+    <mergeCell ref="D212:G212"/>
+    <mergeCell ref="A213:G213"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>

--- a/tests/electrico_nogal_apu.xlsx
+++ b/tests/electrico_nogal_apu.xlsx
@@ -2406,7 +2406,7 @@
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leyenda: fila SIN COLOR = precio de un contrato adjudicado (Nogal 4, 2025) servido en su misma región, o insumos con cotización de proveedor cargada. Fila AMARILLA = precio con APU pero derivado por factor regional o estimado: no está verificado y requiere cotización. Fila ÁMBAR = precio del archivo importado o tecleado a mano, sin APU de respaldo en el catálogo (suma al total y queda declarado). Fila ROJA = ítem sin precio: NO suma al total — un $0 sería un precio inventado.</t>
+          <t xml:space="preserve">Leyenda: fila SIN COLOR = precio de un contrato adjudicado (Nogal 4, 2025) servido en su misma región, insumos con cotización de proveedor cargada, APU de referencia oficial del INVIAS o precio de referencia del IDU (marcados 🔵 en la descripción, con su vigencia). Fila AMARILLA = precio con APU pero derivado por factor regional o estimado: no está verificado y requiere cotización. Fila ÁMBAR = precio del archivo importado o tecleado a mano, sin APU de respaldo en el catálogo (suma al total y queda declarado). Fila ROJA = ítem sin precio: NO suma al total — un $0 sería un precio inventado.</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $6.332 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $11.359 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $6.332 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $117.517 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
@@ -2836,135 +2836,128 @@
         <v>81852</v>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $223.323 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.9 · Suministro e instalación de breaker tipo enchufable de 1x20 A.</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E36" s="16">
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E37" s="16">
         <v>32908</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $70.851 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.10 · Suministro de tablero metálico trifásico de 18 circuitos  con espacio para totalizador.</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E40" s="16">
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E41" s="16">
         <v>3129564</v>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $335.847 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.11 · Desconexión, desmonte y retiro tablero existente</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: GBL</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E43" s="16">
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E45" s="16">
         <v>1529364</v>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.12 · Marquillaje e identificación</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIDAD: GBL</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E46" s="16">
-        <v>2493992</v>
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $120.470 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
       </c>
     </row>
     <row r="47"/>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2,1,1 · Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
+          <t xml:space="preserve">1.12 · Marquillaje e identificación</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIDAD: UND</t>
+          <t xml:space="preserve">UNIDAD: GBL</t>
         </is>
       </c>
     </row>
@@ -2980,540 +2973,540 @@
         </is>
       </c>
       <c r="E49" s="16">
+        <v>2493992</v>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,1,1 · Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIDAD: UND</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E52" s="16">
         <v>312864</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2.2.1 · Suministro e instalación de interruptor sencill, tubo eMT de 1/2", caja metálica tipo radwell, cable de cobre No 12 AWG LSZH, conector tipo resorte o emplame autodesforre, accesorios y elemntos de fijación,</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E53" s="16">
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E56" s="16">
         <v>301516</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $165.880 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2,2,2 · Suministro e instalación de interruptor doble, tubo EMT de 1/2", caja metálica tipo Radwell, cable No 12 AWG LSZH, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación,  transporte, aseo diario.</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E57" s="16">
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E60" s="16">
         <v>309032</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2,2,2 · Suministro e instalación de interruptor triple, tubo EMT de 1/2", caja metálica tipo Radwell, cable No 12 AWG LSZH, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación,  transporte, aseo diario.</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D61" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E61" s="16">
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E64" s="16">
         <v>320460</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2,3,1 · Luminaria LED 120x30 Cm 40 W Sylvania Ref. P28399-41, marco metálico pintura electrostática color blanco, accesotios, elementos de fijación y trasporte.</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E65" s="16">
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E68" s="16">
         <v>153584</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $195.719 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,3,3 · Luminaria LED 60x60 Cm 40 W Sylvania Ref. P27916, marco metálico pintura electrostática color blanco, accesotios, elementos de fijación y anclaje, trasporte.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIDAD: UND</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E72" s="16">
+        <v>131640</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $137.445 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2,3,3 · Luminaria LED 60x60 Cm 40 W Sylvania Ref. P27916, marco metálico pintura electrostática color blanco, accesotios, elementos de fijación y anclaje, trasporte.</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIDAD: UND</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D69" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E69" s="16">
-        <v>131640</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $137.445 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.1 · Suministro e instalación de tomacoriente monofásica normal de 15 A 120 V en canaleta metálica. Incluye: troquel metálico para toma eléctrica, cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje,
 transporte, marquilla de identificación y aseo diario.</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E73" s="16">
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E76" s="16">
         <v>320488</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="17" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.2 · Suministro e instalación de canaleta metalica calibre 20-22 con división, pintura electrostática de 15x5 cm, color blanca.</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E77" s="16">
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E80" s="16">
         <v>74596</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="17" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $122.568 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.3 · Suministro e instalación de cable de cobre 3x12 trenzado AWG  LSZH azul</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E81" s="16">
+    <row r="84">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E84" s="16">
         <v>30172</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $6.332 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.4 · Suministro e instalación de cable de cobre No 12 AWG LSZH</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E85" s="16">
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E88" s="16">
         <v>17552</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87"/>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $6.332 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.5 · Suministro e instalación de alambre de cobre desnudo No 14 AWG</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D89" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E89" s="16">
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E92" s="16">
         <v>14928</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91"/>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $117.517 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.6 · Suministro e instalación de breaker tipo industrial de 3x40 A.</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E93" s="16">
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E96" s="16">
         <v>81852</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $123.053 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $1.429.794 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.7 · Suministro e instalación de breaker tipo enchufable de 3x20 A.</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D97" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E97" s="16">
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E100" s="16">
         <v>55152</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="17" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $70.851 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.8 · Suministro e instalación de breaker tipo enchufable de 1x20 A.</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E101" s="16">
+    <row r="104">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E104" s="16">
         <v>41688</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="17" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $70.851 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="103"/>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="106"/>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.9 · Suministro e instalación de breaker tipo riel de 3x40 A.</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E105" s="16">
+    <row r="108">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E108" s="16">
         <v>81852</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $123.053 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107"/>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.10 · Suministro de tablero metálico trifásico de 18 circuitos con espacio para totalizador</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIDAD: UND</t>
-        </is>
-      </c>
-    </row>
     <row r="109">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D109" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E109" s="16">
-        <v>3129564</v>
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $69.340 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
       </c>
     </row>
     <row r="110"/>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.11 · Suministro e instalación de caja de paso metálica de 30*30*20 Cm, elementos de fijación y anclaje.</t>
+          <t xml:space="preserve">1.10 · Suministro de tablero metálico trifásico de 18 circuitos con espacio para totalizador</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -3534,327 +3527,328 @@
         </is>
       </c>
       <c r="E112" s="16">
+        <v>3129564</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $335.847 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.11 · Suministro e instalación de caja de paso metálica de 30*30*20 Cm, elementos de fijación y anclaje.</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIDAD: UND</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E116" s="16">
         <v>88536</v>
       </c>
     </row>
-    <row r="113"/>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $575.449 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.12 · Reemplazo tubería sobrepuesta PVC existente de 2" en costado occidental por tubería EMT de 2", incluye unionesy terminales en EMT 2"</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E115" s="16">
+    <row r="120">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E120" s="16">
         <v>133824</v>
       </c>
     </row>
-    <row r="116"/>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $151.280 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.13 · Instalación tubería sobrepuesta de 1 1/2" entre caja de paso existente y caja de paso nueva, incluye uniones y terminales en EMT 1 1/2"</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E118" s="16">
+    <row r="124">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E124" s="16">
         <v>114616</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $53.199 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120"/>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $151.280 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.14 · Regata en muro tubería de 1 1/2"</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E122" s="16">
+    <row r="128">
+      <c r="A128" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E128" s="16">
         <v>52956</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $77.939 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124"/>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $53.361 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.15 · Regata en piso tubería de 1 1/2"</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E126" s="16">
+    <row r="132">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E132" s="16">
         <v>57040</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $77.939 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128"/>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $16.075 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134"/>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.16 · Acometida entre Tablero principal y Tablero Eléctrico Sala de Música en cable de cobre No 6 AWG LSZH. 3 fases y neutro</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D130" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E130" s="16">
+    <row r="136">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E136" s="16">
         <v>47044</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="17" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $40.180 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="132"/>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="138"/>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.17 · Acometida entre Tablero principal y Tablero Eléctrico Sala de Música en cable de cobre No 10 AWG LSZH. Tierra</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D134" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E134" s="16">
+    <row r="140">
+      <c r="A140" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E140" s="16">
         <v>36656</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="17" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $122.568 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="136"/>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="142"/>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.18 · Desalambrado y realambrado de acometida existente por cambio de tubería.</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: GBL</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E138" s="16">
+    <row r="144">
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E144" s="16">
         <v>2712980</v>
       </c>
     </row>
-    <row r="139"/>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $35.369 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146"/>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2,1,1 · Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D141" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E141" s="16">
+    <row r="148">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E148" s="16">
         <v>312864</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="17" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143"/>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2,2,2 · Suministro e instalación de interruptor triple, tubo EMT de 3/4", caja metálica tipo Radwell, cable No 12 aWG LSZH, conector tipo resorte o empalme autodesforre, transporte, aseo diario.</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIDAD: UND</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D145" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E145" s="16">
-        <v>320460</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147"/>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2,3,1 · PENDIENTE-POSIBLE USO DE RIEL Y LUMINARIA SYLVANIA</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIDAD: UND</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⛔ SIN PRECIO — «PENDIENTE-POSIBLE USO DE RIEL Y LUMINARIA SYLVANIA» no casa con ningún ítem del catálogo y no trae precio: escriba su precio unitario o asígnele un ítem. Sin precio NO suma al total — un 0 sería un precio inventado.</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3856,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1 · Suministro e instalación de tomacoriente monofásica de 15 A 120 V, en muro, tubo PVC 1", tubo PVC 1/2", caja metálica Ref. 5800,  cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje, transporte,  marquilla de identificación y aseo diario.</t>
+          <t xml:space="preserve">2,2,2 · Suministro e instalación de interruptor triple, tubo EMT de 3/4", caja metálica tipo Radwell, cable No 12 aWG LSZH, conector tipo resorte o empalme autodesforre, transporte, aseo diario.</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -3883,7 +3877,7 @@
         </is>
       </c>
       <c r="E152" s="16">
-        <v>613836</v>
+        <v>320460</v>
       </c>
     </row>
     <row r="153">
@@ -3897,391 +3891,383 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2,3,1 · PENDIENTE-POSIBLE USO DE RIEL Y LUMINARIA SYLVANIA</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIDAD: UND</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⛔ SIN PRECIO — «PENDIENTE-POSIBLE USO DE RIEL Y LUMINARIA SYLVANIA» no casa con ningún ítem del catálogo y no trae precio: escriba su precio unitario o asígnele un ítem. Sin precio NO suma al total — un 0 sería un precio inventado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157"/>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1 · Suministro e instalación de tomacoriente monofásica de 15 A 120 V, en muro, tubo PVC 1", tubo PVC 1/2", caja metálica Ref. 5800,  cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje, transporte,  marquilla de identificación y aseo diario.</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIDAD: UND</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E159" s="16">
+        <v>613836</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161"/>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2,1,1 · Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D156" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E156" s="16">
+    <row r="163">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E163" s="16">
         <v>312864</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="17" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="158"/>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="165"/>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2.2.1 · Suministro e instalación de interruptor sencill, tubo eMT de 1/2", caja metálica tipo radwell, cable de cobre No 12 AWG LSZH, conector tipo resorte o emplame autodesforre, accesorios y elemntos de fijación,</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E160" s="16">
+    <row r="167">
+      <c r="A167" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D167" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E167" s="16">
         <v>301516</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="17" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $165.880 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="162"/>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="169"/>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2,3,3 · Luminaria LED 60x60 Cm 40 W Sylvania Ref. P27916, marco metálico pintura electrostática color blanco, accesotios, elementos de fijación y trasporte.</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D164" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E164" s="16">
+    <row r="171">
+      <c r="A171" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D171" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E171" s="16">
         <v>131640</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="17" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $137.445 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="166"/>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="173"/>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.1 · Suministro e instalación de tomacoriente monofásica normal de 15 A 120 V en canaleta metálica. Incluye: troquel metálico para toma eléctrica, cable cobre AWG LSZH 3x12 trenzado azul, emplame autodesforre, accesorios y elementos de fijación y anclaje,
 transporte, marquilla de identificación y aseo diario.</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D168" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E168" s="16">
+    <row r="175">
+      <c r="A175" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D175" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E175" s="16">
         <v>320488</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="17" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="170"/>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="177"/>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.2 · Suministro e instalación de canaleta metalica calibre 20-22 con división, pintura electrostática de 15x5 cm, color blanca.</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D172" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E172" s="16">
+    <row r="179">
+      <c r="A179" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D179" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E179" s="16">
         <v>74596</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="17" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $122.568 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="174"/>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="181"/>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.3 · Suministro e instalación de cable de cobre 3x12 trenzado AWG  LSZH azul</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D176" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E176" s="16">
+    <row r="183">
+      <c r="A183" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D183" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E183" s="16">
         <v>30172</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178"/>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $6.332 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185"/>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.4 · Suministro e instalación de cable de cobre No 12 AWG LSZH</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D180" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E180" s="16">
+    <row r="187">
+      <c r="A187" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D187" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E187" s="16">
         <v>17552</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182"/>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $6.332 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189"/>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.5 · Suministro e instalación de alambre de cobre desnudo No 14 AWG</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: ML</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D184" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E184" s="16">
+    <row r="191">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D191" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E191" s="16">
         <v>14928</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $37.515 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="186"/>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $117.517 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193"/>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1.6 · Suministro e instalación de breaker tipo enchufable de 1x20 A.</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D188" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E188" s="16">
+    <row r="195">
+      <c r="A195" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D195" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E195" s="16">
         <v>41688</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="17" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $70.851 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
-      </c>
-    </row>
-    <row r="190"/>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.7 · Desconexión, deslambrado  de acometida existente para cambio tablero existente.</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIDAD: GBL</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D192" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E192" s="16">
-        <v>1929244</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $2.302.607 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194"/>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.8 · Alambrado, traslado y reconexión de red eléctrica existente a nuevo tablero eléctrico.</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIDAD: GBL</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D196" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E196" s="16">
-        <v>3259128</v>
       </c>
     </row>
     <row r="197"/>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2,1,1 · Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
+          <t xml:space="preserve">1.7 · Desconexión, deslambrado  de acometida existente para cambio tablero existente.</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIDAD: UND</t>
+          <t xml:space="preserve">UNIDAD: GBL</t>
         </is>
       </c>
     </row>
@@ -4297,13 +4283,13 @@
         </is>
       </c>
       <c r="E199" s="16">
-        <v>312864</v>
+        <v>1929244</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $2.302.607 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
@@ -4311,12 +4297,12 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2,2,2 · Suministro e instalación de interruptor triple, tubo EMT de 3/4", caja metálica tipo Radwell, cable No 12 aWG LSZH, conector tipo resorte o empalme autodesforre, transporte, aseo diario.</t>
+          <t xml:space="preserve">1.8 · Alambrado, traslado y reconexión de red eléctrica existente a nuevo tablero eléctrico.</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIDAD: UND</t>
+          <t xml:space="preserve">UNIDAD: GBL</t>
         </is>
       </c>
     </row>
@@ -4332,86 +4318,149 @@
         </is>
       </c>
       <c r="E203" s="16">
+        <v>3259128</v>
+      </c>
+    </row>
+    <row r="204"/>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,1,1 · Suministro e instalación tubo EMT de 1/2", caja octogonal, cable de cobre aislado No 12 AWG LSZH, tomacorriente monofásica, conector tipo resorte o empalme autodesforre, accesorios y elementos de fijación, transporte, alquiler andamio, armado y desarmado y aseo diario.</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIDAD: UND</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E206" s="16">
+        <v>312864</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208"/>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,2,2 · Suministro e instalación de interruptor triple, tubo EMT de 3/4", caja metálica tipo Radwell, cable No 12 aWG LSZH, conector tipo resorte o empalme autodesforre, transporte, aseo diario.</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIDAD: UND</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E210" s="16">
         <v>320460</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="17" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $183.729 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="205"/>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="212"/>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2,3,1 · Luminaria panel LED 120*30 Cm Sylvania Ref. P27916-41</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIDAD: UND</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
-        </is>
-      </c>
-      <c r="D207" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VR UNITARIO =</t>
-        </is>
-      </c>
-      <c r="E207" s="16">
+    <row r="214">
+      <c r="A214" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRECIO SEGÚN ARCHIVO IMPORTADO — SIN APU DE RESPALDO EN EL CATÁLOGO</t>
+        </is>
+      </c>
+      <c r="D214" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR UNITARIO =</t>
+        </is>
+      </c>
+      <c r="E214" s="16">
         <v>153584</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="17" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Referencia del catálogo para este ítem: $137.445 de costo directo. El precio del archivo MANDA; la diferencia queda declarada aquí para poder discutirla.</t>
         </is>
       </c>
     </row>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizó y elaboró los APU:</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Firma:</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Nombre / Matrícula profesional:</t>
         </is>
       </c>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="D219" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="17" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Los factores de cada línea (cantidad base, desperdicio, rendimiento, distancia y recargo prestacional) van en las columnas F y G para que el análisis se pueda auditar sin leer la descripción.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="159">
+  <mergeCells count="166">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:D4"/>
@@ -4437,140 +4486,147 @@
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:G46"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A90:G90"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A94:G94"/>
-    <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A98:G98"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A102:G102"/>
-    <mergeCell ref="A104:D104"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A106:G106"/>
-    <mergeCell ref="A108:D108"/>
-    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A85:G85"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A89:G89"/>
+    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A101:G101"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A105:G105"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A109:G109"/>
     <mergeCell ref="A111:D111"/>
     <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A119:G119"/>
-    <mergeCell ref="A121:D121"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A123:G123"/>
-    <mergeCell ref="A125:D125"/>
-    <mergeCell ref="A126:C126"/>
-    <mergeCell ref="A127:G127"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A130:C130"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A133:D133"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A135:G135"/>
-    <mergeCell ref="A137:D137"/>
-    <mergeCell ref="A138:C138"/>
-    <mergeCell ref="A140:D140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A142:G142"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A146:G146"/>
-    <mergeCell ref="A148:D148"/>
+    <mergeCell ref="A113:G113"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A117:G117"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A121:G121"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A125:G125"/>
+    <mergeCell ref="A127:D127"/>
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A129:G129"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="A133:G133"/>
+    <mergeCell ref="A135:D135"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A137:G137"/>
+    <mergeCell ref="A139:D139"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:G141"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A145:G145"/>
+    <mergeCell ref="A147:D147"/>
+    <mergeCell ref="A148:C148"/>
     <mergeCell ref="A149:G149"/>
     <mergeCell ref="A151:D151"/>
     <mergeCell ref="A152:C152"/>
     <mergeCell ref="A153:G153"/>
     <mergeCell ref="A155:D155"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A157:G157"/>
-    <mergeCell ref="A159:D159"/>
-    <mergeCell ref="A160:C160"/>
-    <mergeCell ref="A161:G161"/>
-    <mergeCell ref="A163:D163"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:G165"/>
-    <mergeCell ref="A167:D167"/>
-    <mergeCell ref="A168:C168"/>
-    <mergeCell ref="A169:G169"/>
-    <mergeCell ref="A171:D171"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:G173"/>
-    <mergeCell ref="A175:D175"/>
-    <mergeCell ref="A176:C176"/>
-    <mergeCell ref="A177:G177"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:G181"/>
-    <mergeCell ref="A183:D183"/>
-    <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A185:G185"/>
-    <mergeCell ref="A187:D187"/>
-    <mergeCell ref="A188:C188"/>
-    <mergeCell ref="A189:G189"/>
-    <mergeCell ref="A191:D191"/>
-    <mergeCell ref="A192:C192"/>
-    <mergeCell ref="A193:G193"/>
-    <mergeCell ref="A195:D195"/>
-    <mergeCell ref="A196:C196"/>
+    <mergeCell ref="A156:G156"/>
+    <mergeCell ref="A158:D158"/>
+    <mergeCell ref="A159:C159"/>
+    <mergeCell ref="A160:G160"/>
+    <mergeCell ref="A162:D162"/>
+    <mergeCell ref="A163:C163"/>
+    <mergeCell ref="A164:G164"/>
+    <mergeCell ref="A166:D166"/>
+    <mergeCell ref="A167:C167"/>
+    <mergeCell ref="A168:G168"/>
+    <mergeCell ref="A170:D170"/>
+    <mergeCell ref="A171:C171"/>
+    <mergeCell ref="A172:G172"/>
+    <mergeCell ref="A174:D174"/>
+    <mergeCell ref="A175:C175"/>
+    <mergeCell ref="A176:G176"/>
+    <mergeCell ref="A178:D178"/>
+    <mergeCell ref="A179:C179"/>
+    <mergeCell ref="A180:G180"/>
+    <mergeCell ref="A182:D182"/>
+    <mergeCell ref="A183:C183"/>
+    <mergeCell ref="A184:G184"/>
+    <mergeCell ref="A186:D186"/>
+    <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A188:G188"/>
+    <mergeCell ref="A190:D190"/>
+    <mergeCell ref="A191:C191"/>
+    <mergeCell ref="A192:G192"/>
+    <mergeCell ref="A194:D194"/>
+    <mergeCell ref="A195:C195"/>
+    <mergeCell ref="A196:G196"/>
     <mergeCell ref="A198:D198"/>
     <mergeCell ref="A199:C199"/>
     <mergeCell ref="A200:G200"/>
     <mergeCell ref="A202:D202"/>
     <mergeCell ref="A203:C203"/>
-    <mergeCell ref="A204:G204"/>
-    <mergeCell ref="A206:D206"/>
-    <mergeCell ref="A207:C207"/>
-    <mergeCell ref="A208:G208"/>
-    <mergeCell ref="A211:C211"/>
-    <mergeCell ref="D211:G211"/>
-    <mergeCell ref="A212:C212"/>
-    <mergeCell ref="D212:G212"/>
-    <mergeCell ref="A213:G213"/>
+    <mergeCell ref="A205:D205"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A207:G207"/>
+    <mergeCell ref="A209:D209"/>
+    <mergeCell ref="A210:C210"/>
+    <mergeCell ref="A211:G211"/>
+    <mergeCell ref="A213:D213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A215:G215"/>
+    <mergeCell ref="A218:C218"/>
+    <mergeCell ref="D218:G218"/>
+    <mergeCell ref="A219:C219"/>
+    <mergeCell ref="D219:G219"/>
+    <mergeCell ref="A220:G220"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
